--- a/docs/pension_data_combined_2026-10-08.xlsx
+++ b/docs/pension_data_combined_2026-10-08.xlsx
@@ -1228,7 +1228,7 @@
         <v>1.1941</v>
       </c>
       <c r="D48" t="n">
-        <v>3957852.65</v>
+        <v>3962626.22</v>
       </c>
     </row>
     <row r="49">
@@ -1246,7 +1246,7 @@
         <v>2.2238</v>
       </c>
       <c r="D49" t="n">
-        <v>65164676.79</v>
+        <v>65178244.36</v>
       </c>
     </row>
     <row r="50">
@@ -1264,7 +1264,7 @@
         <v>2.2446</v>
       </c>
       <c r="D50" t="n">
-        <v>214038934.22</v>
+        <v>214011153.08</v>
       </c>
     </row>
     <row r="51">
@@ -1282,7 +1282,7 @@
         <v>2.2655</v>
       </c>
       <c r="D51" t="n">
-        <v>329440752.29</v>
+        <v>329406097.38</v>
       </c>
     </row>
     <row r="52">
@@ -1300,7 +1300,7 @@
         <v>2.2706</v>
       </c>
       <c r="D52" t="n">
-        <v>401864218.52</v>
+        <v>401826246.82</v>
       </c>
     </row>
     <row r="53">
@@ -1318,7 +1318,7 @@
         <v>1.9989</v>
       </c>
       <c r="D53" t="n">
-        <v>366077450.74</v>
+        <v>366088662.56</v>
       </c>
     </row>
     <row r="54">
@@ -1336,7 +1336,7 @@
         <v>1.5334</v>
       </c>
       <c r="D54" t="n">
-        <v>299319947.21</v>
+        <v>299053327.53</v>
       </c>
     </row>
     <row r="55">
@@ -1354,7 +1354,7 @@
         <v>1.1847</v>
       </c>
       <c r="D55" t="n">
-        <v>55925182.08</v>
+        <v>55874989.97</v>
       </c>
     </row>
   </sheetData>

--- a/docs/pension_data_combined_2026-10-08.xlsx
+++ b/docs/pension_data_combined_2026-10-08.xlsx
@@ -1224,9 +1224,6 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>1.1941</v>
-      </c>
       <c r="D48" t="n">
         <v>3962626.22</v>
       </c>
@@ -1349,9 +1346,6 @@
         <is>
           <t>2026-10-08</t>
         </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1.1847</v>
       </c>
       <c r="D55" t="n">
         <v>55874989.97</v>
